--- a/src/puzzles.xlsx
+++ b/src/puzzles.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11003"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/a91971/Desktop/CHESSPECKER/chess-trainer/src/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98A49B76-DF16-F448-8B53-DF7DA710CD71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="28800" yWindow="-5640" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="61">
   <si>
     <t>PuzzleId</t>
   </si>
@@ -202,8 +208,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -266,13 +272,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -310,7 +324,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -344,6 +358,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -378,9 +393,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -553,11 +569,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J51"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -589,7 +605,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -618,7 +634,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -647,7 +663,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -676,7 +692,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -708,7 +724,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -737,7 +753,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -766,7 +782,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -795,7 +811,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -824,7 +840,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -853,7 +869,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -882,6 +898,1190 @@
         <v>58</v>
       </c>
       <c r="J11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12">
+        <v>2037</v>
+      </c>
+      <c r="F12">
+        <v>77</v>
+      </c>
+      <c r="G12">
+        <v>95</v>
+      </c>
+      <c r="H12">
+        <v>9125</v>
+      </c>
+      <c r="I12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13">
+        <v>1455</v>
+      </c>
+      <c r="F13">
+        <v>74</v>
+      </c>
+      <c r="G13">
+        <v>96</v>
+      </c>
+      <c r="H13">
+        <v>35537</v>
+      </c>
+      <c r="I13" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14">
+        <v>1356</v>
+      </c>
+      <c r="F14">
+        <v>78</v>
+      </c>
+      <c r="G14">
+        <v>91</v>
+      </c>
+      <c r="H14">
+        <v>750</v>
+      </c>
+      <c r="I14" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15">
+        <v>1103</v>
+      </c>
+      <c r="F15">
+        <v>74</v>
+      </c>
+      <c r="G15">
+        <v>88</v>
+      </c>
+      <c r="H15">
+        <v>604</v>
+      </c>
+      <c r="I15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16">
+        <v>1542</v>
+      </c>
+      <c r="F16">
+        <v>75</v>
+      </c>
+      <c r="G16">
+        <v>92</v>
+      </c>
+      <c r="H16">
+        <v>621</v>
+      </c>
+      <c r="I16" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17">
+        <v>1481</v>
+      </c>
+      <c r="F17">
+        <v>75</v>
+      </c>
+      <c r="G17">
+        <v>97</v>
+      </c>
+      <c r="H17">
+        <v>732</v>
+      </c>
+      <c r="I17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18">
+        <v>2861</v>
+      </c>
+      <c r="F18">
+        <v>108</v>
+      </c>
+      <c r="G18">
+        <v>85</v>
+      </c>
+      <c r="H18">
+        <v>276</v>
+      </c>
+      <c r="I18" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19">
+        <v>1592</v>
+      </c>
+      <c r="F19">
+        <v>79</v>
+      </c>
+      <c r="G19">
+        <v>75</v>
+      </c>
+      <c r="H19">
+        <v>109</v>
+      </c>
+      <c r="I19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20" t="s">
+        <v>48</v>
+      </c>
+      <c r="E20">
+        <v>1376</v>
+      </c>
+      <c r="F20">
+        <v>75</v>
+      </c>
+      <c r="G20">
+        <v>86</v>
+      </c>
+      <c r="H20">
+        <v>651</v>
+      </c>
+      <c r="I20" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" t="s">
+        <v>49</v>
+      </c>
+      <c r="E21">
+        <v>1414</v>
+      </c>
+      <c r="F21">
+        <v>78</v>
+      </c>
+      <c r="G21">
+        <v>75</v>
+      </c>
+      <c r="H21">
+        <v>526</v>
+      </c>
+      <c r="I21" t="s">
+        <v>58</v>
+      </c>
+      <c r="J21" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>10</v>
+      </c>
+      <c r="B22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" t="s">
+        <v>40</v>
+      </c>
+      <c r="E22">
+        <v>2037</v>
+      </c>
+      <c r="F22">
+        <v>77</v>
+      </c>
+      <c r="G22">
+        <v>95</v>
+      </c>
+      <c r="H22">
+        <v>9125</v>
+      </c>
+      <c r="I22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23">
+        <v>1455</v>
+      </c>
+      <c r="F23">
+        <v>74</v>
+      </c>
+      <c r="G23">
+        <v>96</v>
+      </c>
+      <c r="H23">
+        <v>35537</v>
+      </c>
+      <c r="I23" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" t="s">
+        <v>42</v>
+      </c>
+      <c r="E24">
+        <v>1356</v>
+      </c>
+      <c r="F24">
+        <v>78</v>
+      </c>
+      <c r="G24">
+        <v>91</v>
+      </c>
+      <c r="H24">
+        <v>750</v>
+      </c>
+      <c r="I24" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25">
+        <v>1103</v>
+      </c>
+      <c r="F25">
+        <v>74</v>
+      </c>
+      <c r="G25">
+        <v>88</v>
+      </c>
+      <c r="H25">
+        <v>604</v>
+      </c>
+      <c r="I25" t="s">
+        <v>53</v>
+      </c>
+      <c r="J25" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" t="s">
+        <v>44</v>
+      </c>
+      <c r="E26">
+        <v>1542</v>
+      </c>
+      <c r="F26">
+        <v>75</v>
+      </c>
+      <c r="G26">
+        <v>92</v>
+      </c>
+      <c r="H26">
+        <v>621</v>
+      </c>
+      <c r="I26" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" t="s">
+        <v>35</v>
+      </c>
+      <c r="D27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27">
+        <v>1481</v>
+      </c>
+      <c r="F27">
+        <v>75</v>
+      </c>
+      <c r="G27">
+        <v>97</v>
+      </c>
+      <c r="H27">
+        <v>732</v>
+      </c>
+      <c r="I27" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" t="s">
+        <v>36</v>
+      </c>
+      <c r="D28" t="s">
+        <v>46</v>
+      </c>
+      <c r="E28">
+        <v>2861</v>
+      </c>
+      <c r="F28">
+        <v>108</v>
+      </c>
+      <c r="G28">
+        <v>85</v>
+      </c>
+      <c r="H28">
+        <v>276</v>
+      </c>
+      <c r="I28" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" t="s">
+        <v>37</v>
+      </c>
+      <c r="D29" t="s">
+        <v>47</v>
+      </c>
+      <c r="E29">
+        <v>1592</v>
+      </c>
+      <c r="F29">
+        <v>79</v>
+      </c>
+      <c r="G29">
+        <v>75</v>
+      </c>
+      <c r="H29">
+        <v>109</v>
+      </c>
+      <c r="I29" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>18</v>
+      </c>
+      <c r="B30" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30" t="s">
+        <v>38</v>
+      </c>
+      <c r="D30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E30">
+        <v>1376</v>
+      </c>
+      <c r="F30">
+        <v>75</v>
+      </c>
+      <c r="G30">
+        <v>86</v>
+      </c>
+      <c r="H30">
+        <v>651</v>
+      </c>
+      <c r="I30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>19</v>
+      </c>
+      <c r="B31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31" t="s">
+        <v>49</v>
+      </c>
+      <c r="E31">
+        <v>1414</v>
+      </c>
+      <c r="F31">
+        <v>78</v>
+      </c>
+      <c r="G31">
+        <v>75</v>
+      </c>
+      <c r="H31">
+        <v>526</v>
+      </c>
+      <c r="I31" t="s">
+        <v>58</v>
+      </c>
+      <c r="J31" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>10</v>
+      </c>
+      <c r="B32" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" t="s">
+        <v>30</v>
+      </c>
+      <c r="D32" t="s">
+        <v>40</v>
+      </c>
+      <c r="E32">
+        <v>2037</v>
+      </c>
+      <c r="F32">
+        <v>77</v>
+      </c>
+      <c r="G32">
+        <v>95</v>
+      </c>
+      <c r="H32">
+        <v>9125</v>
+      </c>
+      <c r="I32" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33" t="s">
+        <v>21</v>
+      </c>
+      <c r="C33" t="s">
+        <v>31</v>
+      </c>
+      <c r="D33" t="s">
+        <v>41</v>
+      </c>
+      <c r="E33">
+        <v>1455</v>
+      </c>
+      <c r="F33">
+        <v>74</v>
+      </c>
+      <c r="G33">
+        <v>96</v>
+      </c>
+      <c r="H33">
+        <v>35537</v>
+      </c>
+      <c r="I33" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>12</v>
+      </c>
+      <c r="B34" t="s">
+        <v>22</v>
+      </c>
+      <c r="C34" t="s">
+        <v>32</v>
+      </c>
+      <c r="D34" t="s">
+        <v>42</v>
+      </c>
+      <c r="E34">
+        <v>1356</v>
+      </c>
+      <c r="F34">
+        <v>78</v>
+      </c>
+      <c r="G34">
+        <v>91</v>
+      </c>
+      <c r="H34">
+        <v>750</v>
+      </c>
+      <c r="I34" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B35" t="s">
+        <v>23</v>
+      </c>
+      <c r="C35" t="s">
+        <v>33</v>
+      </c>
+      <c r="D35" t="s">
+        <v>43</v>
+      </c>
+      <c r="E35">
+        <v>1103</v>
+      </c>
+      <c r="F35">
+        <v>74</v>
+      </c>
+      <c r="G35">
+        <v>88</v>
+      </c>
+      <c r="H35">
+        <v>604</v>
+      </c>
+      <c r="I35" t="s">
+        <v>53</v>
+      </c>
+      <c r="J35" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>14</v>
+      </c>
+      <c r="B36" t="s">
+        <v>24</v>
+      </c>
+      <c r="C36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D36" t="s">
+        <v>44</v>
+      </c>
+      <c r="E36">
+        <v>1542</v>
+      </c>
+      <c r="F36">
+        <v>75</v>
+      </c>
+      <c r="G36">
+        <v>92</v>
+      </c>
+      <c r="H36">
+        <v>621</v>
+      </c>
+      <c r="I36" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" t="s">
+        <v>35</v>
+      </c>
+      <c r="D37" t="s">
+        <v>45</v>
+      </c>
+      <c r="E37">
+        <v>1481</v>
+      </c>
+      <c r="F37">
+        <v>75</v>
+      </c>
+      <c r="G37">
+        <v>97</v>
+      </c>
+      <c r="H37">
+        <v>732</v>
+      </c>
+      <c r="I37" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>16</v>
+      </c>
+      <c r="B38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C38" t="s">
+        <v>36</v>
+      </c>
+      <c r="D38" t="s">
+        <v>46</v>
+      </c>
+      <c r="E38">
+        <v>2861</v>
+      </c>
+      <c r="F38">
+        <v>108</v>
+      </c>
+      <c r="G38">
+        <v>85</v>
+      </c>
+      <c r="H38">
+        <v>276</v>
+      </c>
+      <c r="I38" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>17</v>
+      </c>
+      <c r="B39" t="s">
+        <v>27</v>
+      </c>
+      <c r="C39" t="s">
+        <v>37</v>
+      </c>
+      <c r="D39" t="s">
+        <v>47</v>
+      </c>
+      <c r="E39">
+        <v>1592</v>
+      </c>
+      <c r="F39">
+        <v>79</v>
+      </c>
+      <c r="G39">
+        <v>75</v>
+      </c>
+      <c r="H39">
+        <v>109</v>
+      </c>
+      <c r="I39" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>18</v>
+      </c>
+      <c r="B40" t="s">
+        <v>28</v>
+      </c>
+      <c r="C40" t="s">
+        <v>38</v>
+      </c>
+      <c r="D40" t="s">
+        <v>48</v>
+      </c>
+      <c r="E40">
+        <v>1376</v>
+      </c>
+      <c r="F40">
+        <v>75</v>
+      </c>
+      <c r="G40">
+        <v>86</v>
+      </c>
+      <c r="H40">
+        <v>651</v>
+      </c>
+      <c r="I40" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>19</v>
+      </c>
+      <c r="B41" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41" t="s">
+        <v>39</v>
+      </c>
+      <c r="D41" t="s">
+        <v>49</v>
+      </c>
+      <c r="E41">
+        <v>1414</v>
+      </c>
+      <c r="F41">
+        <v>78</v>
+      </c>
+      <c r="G41">
+        <v>75</v>
+      </c>
+      <c r="H41">
+        <v>526</v>
+      </c>
+      <c r="I41" t="s">
+        <v>58</v>
+      </c>
+      <c r="J41" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>10</v>
+      </c>
+      <c r="B42" t="s">
+        <v>20</v>
+      </c>
+      <c r="C42" t="s">
+        <v>30</v>
+      </c>
+      <c r="D42" t="s">
+        <v>40</v>
+      </c>
+      <c r="E42">
+        <v>2037</v>
+      </c>
+      <c r="F42">
+        <v>77</v>
+      </c>
+      <c r="G42">
+        <v>95</v>
+      </c>
+      <c r="H42">
+        <v>9125</v>
+      </c>
+      <c r="I42" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>11</v>
+      </c>
+      <c r="B43" t="s">
+        <v>21</v>
+      </c>
+      <c r="C43" t="s">
+        <v>31</v>
+      </c>
+      <c r="D43" t="s">
+        <v>41</v>
+      </c>
+      <c r="E43">
+        <v>1455</v>
+      </c>
+      <c r="F43">
+        <v>74</v>
+      </c>
+      <c r="G43">
+        <v>96</v>
+      </c>
+      <c r="H43">
+        <v>35537</v>
+      </c>
+      <c r="I43" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" t="s">
+        <v>22</v>
+      </c>
+      <c r="C44" t="s">
+        <v>32</v>
+      </c>
+      <c r="D44" t="s">
+        <v>42</v>
+      </c>
+      <c r="E44">
+        <v>1356</v>
+      </c>
+      <c r="F44">
+        <v>78</v>
+      </c>
+      <c r="G44">
+        <v>91</v>
+      </c>
+      <c r="H44">
+        <v>750</v>
+      </c>
+      <c r="I44" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>13</v>
+      </c>
+      <c r="B45" t="s">
+        <v>23</v>
+      </c>
+      <c r="C45" t="s">
+        <v>33</v>
+      </c>
+      <c r="D45" t="s">
+        <v>43</v>
+      </c>
+      <c r="E45">
+        <v>1103</v>
+      </c>
+      <c r="F45">
+        <v>74</v>
+      </c>
+      <c r="G45">
+        <v>88</v>
+      </c>
+      <c r="H45">
+        <v>604</v>
+      </c>
+      <c r="I45" t="s">
+        <v>53</v>
+      </c>
+      <c r="J45" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>14</v>
+      </c>
+      <c r="B46" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" t="s">
+        <v>34</v>
+      </c>
+      <c r="D46" t="s">
+        <v>44</v>
+      </c>
+      <c r="E46">
+        <v>1542</v>
+      </c>
+      <c r="F46">
+        <v>75</v>
+      </c>
+      <c r="G46">
+        <v>92</v>
+      </c>
+      <c r="H46">
+        <v>621</v>
+      </c>
+      <c r="I46" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" t="s">
+        <v>35</v>
+      </c>
+      <c r="D47" t="s">
+        <v>45</v>
+      </c>
+      <c r="E47">
+        <v>1481</v>
+      </c>
+      <c r="F47">
+        <v>75</v>
+      </c>
+      <c r="G47">
+        <v>97</v>
+      </c>
+      <c r="H47">
+        <v>732</v>
+      </c>
+      <c r="I47" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>16</v>
+      </c>
+      <c r="B48" t="s">
+        <v>26</v>
+      </c>
+      <c r="C48" t="s">
+        <v>36</v>
+      </c>
+      <c r="D48" t="s">
+        <v>46</v>
+      </c>
+      <c r="E48">
+        <v>2861</v>
+      </c>
+      <c r="F48">
+        <v>108</v>
+      </c>
+      <c r="G48">
+        <v>85</v>
+      </c>
+      <c r="H48">
+        <v>276</v>
+      </c>
+      <c r="I48" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>17</v>
+      </c>
+      <c r="B49" t="s">
+        <v>27</v>
+      </c>
+      <c r="C49" t="s">
+        <v>37</v>
+      </c>
+      <c r="D49" t="s">
+        <v>47</v>
+      </c>
+      <c r="E49">
+        <v>1592</v>
+      </c>
+      <c r="F49">
+        <v>79</v>
+      </c>
+      <c r="G49">
+        <v>75</v>
+      </c>
+      <c r="H49">
+        <v>109</v>
+      </c>
+      <c r="I49" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>18</v>
+      </c>
+      <c r="B50" t="s">
+        <v>28</v>
+      </c>
+      <c r="C50" t="s">
+        <v>38</v>
+      </c>
+      <c r="D50" t="s">
+        <v>48</v>
+      </c>
+      <c r="E50">
+        <v>1376</v>
+      </c>
+      <c r="F50">
+        <v>75</v>
+      </c>
+      <c r="G50">
+        <v>86</v>
+      </c>
+      <c r="H50">
+        <v>651</v>
+      </c>
+      <c r="I50" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>19</v>
+      </c>
+      <c r="B51" t="s">
+        <v>29</v>
+      </c>
+      <c r="C51" t="s">
+        <v>39</v>
+      </c>
+      <c r="D51" t="s">
+        <v>49</v>
+      </c>
+      <c r="E51">
+        <v>1414</v>
+      </c>
+      <c r="F51">
+        <v>78</v>
+      </c>
+      <c r="G51">
+        <v>75</v>
+      </c>
+      <c r="H51">
+        <v>526</v>
+      </c>
+      <c r="I51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J51" t="s">
         <v>60</v>
       </c>
     </row>
